--- a/frontend/Iview Master list update may-26 - Copy.xlsx
+++ b/frontend/Iview Master list update may-26 - Copy.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="78">
   <si>
     <t>P.Sl.No</t>
   </si>
@@ -244,13 +244,22 @@
   </si>
   <si>
     <t>Inhouse-Instruments</t>
+  </si>
+  <si>
+    <t>SPG953/01</t>
+  </si>
+  <si>
+    <t>Is Reference Standard</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +307,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -344,7 +358,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -387,13 +401,61 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Due SOON" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <condense val="0"/>
@@ -784,10 +846,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -875,8 +941,11 @@
       <c r="AC1" s="7" t="s">
         <v>43</v>
       </c>
+      <c r="AD1" s="15" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -930,7 +999,7 @@
       </c>
       <c r="R2" s="5" t="str">
         <f ca="1">IF(ISBLANK(Q2),"NO PLAN",IF(Q2&lt;TODAY(),"OVER DUE",IF(Q2&lt;=TODAY()+3,"DUE SOON","OK")))</f>
-        <v>OK</v>
+        <v>OVER DUE</v>
       </c>
       <c r="S2" s="4"/>
       <c r="T2" s="3"/>
@@ -952,7 +1021,7 @@
       <c r="AB2" s="10"/>
       <c r="AC2" s="10"/>
     </row>
-    <row r="3" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1028,7 +1097,7 @@
       <c r="AB3" s="10"/>
       <c r="AC3" s="10"/>
     </row>
-    <row r="4" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1082,7 +1151,7 @@
       </c>
       <c r="R4" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>OK</v>
+        <v>OVER DUE</v>
       </c>
       <c r="S4" s="11"/>
       <c r="T4" s="3"/>
@@ -1104,7 +1173,7 @@
       <c r="AB4" s="10"/>
       <c r="AC4" s="10"/>
     </row>
-    <row r="5" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1158,7 +1227,7 @@
       </c>
       <c r="R5" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>OK</v>
+        <v>OVER DUE</v>
       </c>
       <c r="S5" s="4"/>
       <c r="T5" s="3"/>
@@ -1180,7 +1249,7 @@
       <c r="AB5" s="10"/>
       <c r="AC5" s="10"/>
     </row>
-    <row r="6" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1234,7 +1303,7 @@
       </c>
       <c r="R6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>OK</v>
+        <v>OVER DUE</v>
       </c>
       <c r="S6" s="4"/>
       <c r="T6" s="3"/>
@@ -1256,7 +1325,7 @@
       <c r="AB6" s="10"/>
       <c r="AC6" s="10"/>
     </row>
-    <row r="7" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1310,7 +1379,7 @@
       </c>
       <c r="R7" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>OK</v>
+        <v>OVER DUE</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="3"/>
@@ -1332,7 +1401,7 @@
       <c r="AB7" s="10"/>
       <c r="AC7" s="10"/>
     </row>
-    <row r="8" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1386,7 +1455,7 @@
       </c>
       <c r="R8" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>OK</v>
+        <v>OVER DUE</v>
       </c>
       <c r="S8" s="4"/>
       <c r="T8" s="3"/>
@@ -1408,7 +1477,7 @@
       <c r="AB8" s="10"/>
       <c r="AC8" s="10"/>
     </row>
-    <row r="9" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1462,7 +1531,7 @@
       </c>
       <c r="R9" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>OK</v>
+        <v>DUE SOON</v>
       </c>
       <c r="S9" s="4"/>
       <c r="T9" s="3"/>
@@ -1484,7 +1553,7 @@
       <c r="AB9" s="10"/>
       <c r="AC9" s="10"/>
     </row>
-    <row r="10" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -1536,7 +1605,7 @@
       </c>
       <c r="R10" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>OK</v>
+        <v>OVER DUE</v>
       </c>
       <c r="S10" s="14"/>
       <c r="T10" s="5">
@@ -1560,43 +1629,139 @@
       <c r="AB10" s="10"/>
       <c r="AC10" s="10"/>
     </row>
+    <row r="11" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P11" s="4">
+        <v>46023</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>46204</v>
+      </c>
+      <c r="R11" s="5" t="str">
+        <f t="shared" ref="R11" ca="1" si="1">IF(ISBLANK(Q11),"NO PLAN",IF(Q11&lt;TODAY(),"OVER DUE",IF(Q11&lt;=TODAY()+7,"DUE SOON","OK")))</f>
+        <v>OVER DUE</v>
+      </c>
+      <c r="S11" s="4"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="R1:R2">
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="DUE SOON">
+    <cfRule type="containsText" dxfId="14" priority="13" operator="containsText" text="DUE SOON">
       <formula>NOT(ISERROR(SEARCH("DUE SOON",R1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="OVER DUE">
+    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="OVER DUE">
       <formula>NOT(ISERROR(SEARCH("OVER DUE",R1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="12" priority="15" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",R1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C2">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C2">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R3:R10">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="DUE SOON">
+    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="DUE SOON">
       <formula>NOT(ISERROR(SEARCH("DUE SOON",R3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="OVER DUE">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="OVER DUE">
       <formula>NOT(ISERROR(SEARCH("OVER DUE",R3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",R3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C10">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C10">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R11">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="DUE SOON">
+      <formula>NOT(ISERROR(SEARCH("DUE SOON",R11)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="OVER DUE">
+      <formula>NOT(ISERROR(SEARCH("OVER DUE",R11)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",R11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C10">
+  <conditionalFormatting sqref="C11">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="O1:O10">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="O1:O11">
       <formula1>$O:$O</formula1>
     </dataValidation>
   </dataValidations>
